--- a/vlearn-app/public/quiz_excel/Day_15_Triển khai thực tế _ Định hướng Enterprise/Day_15_FULL_TOAN_BO_68_CAU.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_15_Triển khai thực tế _ Định hướng Enterprise/Day_15_FULL_TOAN_BO_68_CAU.xlsx
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Hosted TCO=4.000+500+1.200=5.700; self-hosted=3.000+600+2.000+500=6.100; chênh lệch=400 USD/tháng.</t>
+          <t>Hosted TCO: $4.000 + $500 + $1.200 = $5.700. Self-hosted TCO: $3.000 + $600 + $2.000 + $500 = $6.100. Chênh lệch TCO self-hosted trừ hosted: $6.100 - $5.700 = 400 USD/tháng.</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>111111</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Điểm hòa vốn TCO: 500 + 0.04*N = 4500 + 0.004*N =&gt; 0.036*N = 4000 =&gt; N = 4000 / 0.036 ≈ 111,111 request/tháng.</t>
+          <t>Break-even volume: 500 + 0,04*N = 4500 + 0,004*N =&gt; 0,036*N = 4000 =&gt; N = 4000 / 0,036 ≈ 111.111 requests/tháng.</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1303,7 +1303,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính từng option ở cùng volume trước khi trừ.</t>
+          <t>Tại V = 200.000 requests/tháng: Hosted cost = $500 + $0,04 * 200.000 = $500 + $8.000 = $8.500. Self-hosted cost = $4.500 + $0,004 * 200.000 = $4.500 + $800 = $5.300. Self-hosted rẻ hơn hosted: $8.500 - $5.300 = 3.200 USD/tháng.</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1471,7 +1471,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Per request=$0,002+$0,002=$0,004; 1,5 triệu request/tháng ⇒ $6.000.</t>
+          <t>Mỗi request: 1.000 input tokens * $2/M + 200 output tokens * $10/M = $0,002 + $0,002 = $0,004/request. Hàng tháng có 50.000 * 30 = 1.500.000 requests =&gt; Tổng chi phí: 1.500.000 * $0,004 = 6.000 USD/tháng.</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1519,7 +1519,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính input và output subtotal riêng trước khi cộng.</t>
+          <t>Tổng API subtotal: (496 triệu input tokens * $1,5 / triệu) + (186 triệu output tokens * $6 / triệu) = 496 * 1,5 + 186 * 6 = $744 + $1.116 = 1.860 USD/tháng.</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,5</t>
         </is>
       </c>
       <c r="I28" s="4" t="n">
@@ -1929,7 +1929,7 @@
       <c r="J28" s="3" t="n"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một posting gần tên chưa chắc cùng population tuyển dụng.</t>
+          <t>Để so sánh yêu cầu tuyển dụng Data Engineer cấp độ Junior tại Việt Nam trong quý hiện tại, chỉ lấy các bài đăng đúng nhóm đối tượng: (a) Junior Data Engineer tại TP.HCM đăng 2 tuần trước, (b) Junior Data Engineer tại Hà Nội đăng 1 tháng trước, (e) Junior Data Engineer làm remote tại Việt Nam đăng 3 tuần trước.</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I33" s="4" t="n">
@@ -2198,7 +2198,7 @@
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ dùng invariant input, chưa dùng search/route feasibility.</t>
+          <t>Dữ liệu đầu vào vi phạm tính toàn vẹn phải bị loại ngay trước khi chạy thuật toán routing: (a) Thông số vận tốc dùng chung bị xung đột giữa các dòng (0,8 vs 1,0), (b) trùng lặp order_id trong cùng một instance, (c) giá trị nhu cầu không phải là số hợp lệ ('abc').</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -2246,7 +2246,7 @@
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính distance trước rồi chia đúng unit km/phút.</t>
+          <t>Khoảng cách Euclidean từ depot (0,0) tới order (3,4): sqrt(3^2 + 4^2) = sqrt(9 + 16) = 5 km. Thời gian di chuyển với vận tốc 0,5 km/phút: 5 km / 0,5 km/phút = 10 phút.</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -2294,7 +2294,7 @@
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Departure A không bằng arrival A khi có wait/service.</t>
+          <t>Arrival tại A = 4; Ready time A = 10; Service time = 3; Leg A-&gt;B = 2. Do xe đến trước ready time nên phải chờ đến t=10 mới bắt đầu service. Service hoàn tất lúc 10 + 3 = 13. Thời điểm arrival tại B = 13 + 2 = 15.</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -2342,7 +2342,7 @@
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Áp max(0, arrival−due) cho từng order rồi cộng.</t>
+          <t>Lateness từng order: Order A = max(0, 12 - 10) = 2; Order B = max(0, 8 - 9) = 0; Order C = max(0, 20 - 14) = 6. Tổng lateness = 2 + 0 + 6 = 8 phút.</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -2390,7 +2390,7 @@
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính max(0,arrival−due) từng order rồi lấy max.</t>
+          <t>Lateness của 4 orders: Order 1: max(0, 9-10)=0; Order 2: max(0, 15-11)=4; Order 3: max(0, 22-18)=4; Order 4: max(0, 30-31)=0. Maximum lateness = max(0, 4, 4, 0) = 4 phút.</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -2438,7 +2438,7 @@
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Overtime chỉ biết sau khi cộng return leg.</t>
+          <t>Hoàn tất service đơn cuối tại t=52; quay về depot mất 11 phút =&gt; Xe về tới depot lúc 52 + 11 = 63. Shift end = 60 =&gt; Overtime = max(0, 63 - 60) = 3 phút.</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -2486,7 +2486,7 @@
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đừng bắt đầu return leg từ arrival trước service.</t>
+          <t>Đơn cuối arrival lúc t=40, service 8 phút =&gt; Hoàn tất lúc 40 + 8 = 48. Chặng về depot mất 7 phút =&gt; Về depot lúc 48 + 7 = 55. Shift end = 52 =&gt; Overtime = max(0, 55 - 52) = 3 phút.</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -2582,7 +2582,7 @@
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Placeholder rỗng không tính xe.</t>
+          <t>Dung lượng fleet num_vehicles=2. Solution có cấu trúc `[[], [1,2], [], [3]]`. Các mảng rỗng `[]` là placeholder; chỉ có hai route không rỗng là `[1,2]` và `[3]` đại diện cho 2 xe thực sự được sử dụng.</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I45" s="4" t="n">
@@ -2793,7 +2793,7 @@
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So từng dimension trước, chỉ kết luận overall nếu objective được khai báo.</t>
+          <t>So sánh hai lời giải đa mục tiêu khi chưa biết trọng số: (a) B có tổng quãng đường tốt hơn (90 &lt; 100), (b) A dùng ít xe hơn (2 &lt; 3) và trễ giờ ít hơn (5 &lt; 12), (c) không thể kết luận giải pháp nào tối ưu tổng thể nếu chưa có trọng số chính thức, (e) hai lời giải ngang nhau về làm thêm giờ (0) và đơn hàng chưa phục vụ (0).</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -2889,7 +2889,7 @@
       <c r="J47" s="3" t="n"/>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính ratio trước rồi áp cap; invalid/missing mới nhận zero.</t>
+          <t>Raw score = 100 * (reference cost / team cost) = 100 * (120 / 60) = 200. Áp dụng trần cap=150: min(150, 200) = 150 điểm.</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -2937,7 +2937,7 @@
       <c r="J48" s="3" t="n"/>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Cap chỉ tác động khi raw ratio vượt 150.</t>
+          <t>Raw score = 100 * (reference cost / team cost) = 100 * (80 / 100) = 80. Áp dụng cap=150: min(150, 80) = 80 điểm.</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -2985,7 +2985,7 @@
       <c r="J49" s="3" t="n"/>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Score 100 nghĩa bằng reference cost.</t>
+          <t>Score = min(150, 100 * reference / team) = min(150, 100 * (100 / 200)) = min(150, 50) = 50 điểm.</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -3033,7 +3033,7 @@
       <c r="J50" s="3" t="n"/>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ lấy private instance theo contract.</t>
+          <t>Điểm chính thức xếp hạng chỉ tính trên các private instance theo quy định: (120 + 90 + 150) / 3 = 360 / 3 = 120 điểm.</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -3081,7 +3081,7 @@
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số gồm toàn bộ private instance bắt buộc.</t>
+          <t>Điểm trung bình private của cả 4 instances bắt buộc (kể cả instance thiếu bị 0 điểm): (150 + 110 + 0 + 90) / 4 = 350 / 4 = 87,5 điểm.</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -3184,7 +3184,7 @@
       <c r="J53" s="3" t="n"/>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không dùng distance-only delta nếu working cost còn term downstream.</t>
+          <t>Các vị trí chèn khả thi có working-cost delta lần lượt là 12, 7, 9. Delta nhỏ nhất của cheapest feasible insertion là min(12, 7, 9) = 7.</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -3328,7 +3328,7 @@
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính chênh second-best trừ best cho từng order.</t>
+          <t>Regret = second-best insertion cost - best insertion cost. Order A: 9 - 4 = 5; Order B: 20 - 6 = 14; Order C: 11 - 5 = 6. Regret lớn nhất = max(5, 14, 6) = 14.</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I59" s="4" t="n">
@@ -3486,7 +3486,7 @@
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính load mỗi route sau swap, không chỉ tổng toàn fleet.</t>
+          <t>Đánh giá bước hoán đổi (swap): (a) Tải trọng mới của R1 là 10 - 8 + 2 = 4, của R2 là 6 - 2 + 8 = 12; (b) Lời giải bị vi phạm ràng buộc cứng (hard-invalid) vì R2 bị quá tải 2 đơn vị (12 &gt; capacity 10); (c) Mức giảm quãng đường không thể bù đắp vi phạm ràng buộc tải trọng cứng.</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.607</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -3645,7 +3645,7 @@
       <c r="J62" s="3" t="n"/>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Move tốt hơn nhận trực tiếp; move xấu dùng exponent âm.</t>
+          <t>Xác suất chấp nhận move xấu trong Simulated Annealing: P = exp(-Δ / T) = exp(-5 / 10) = exp(-0,5) ≈ 0,60653..., làm tròn 3 chữ số là 0,607.</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -3747,7 +3747,7 @@
       <c r="J64" s="3" t="n"/>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Trừ end-to-end reserve trước khi chia cho instance.</t>
+          <t>Tổng thời gian 30 phút, trừ thời gian dự phòng cố định (reserve) 6 phút, còn lại 30 - 6 = 24 phút. Chia đều cho 8 instances: 24 / 8 = 3 phút/instance.</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -3795,7 +3795,7 @@
       <c r="J65" s="3" t="n"/>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Trừ mọi reserve end-to-end trước khi chia.</t>
+          <t>Tổng thời gian 42 phút. Tổng reserve: 7 phút cố định + 5 phút riêng cho instance cuối = 12 phút. Thời gian còn lại cho 4 instances đầu: 42 - 12 = 30 phút. Chia đều cho 4 instances: 30 / 4 = 7,5 phút/instance.</t>
         </is>
       </c>
     </row>
